--- a/website/app/dashboard/components/Kostentabelle.xlsx
+++ b/website/app/dashboard/components/Kostentabelle.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB88DA20-40EB-4C28-922D-F55530826D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B80EF1-0C95-4B05-9B5A-8E705D5B5FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-7425" windowWidth="16440" windowHeight="29040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16200" yWindow="375" windowWidth="16410" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -40,9 +40,6 @@
   </si>
   <si>
     <t xml:space="preserve">Passwort </t>
-  </si>
-  <si>
-    <t>test</t>
   </si>
   <si>
     <t>Geld eingezahlt</t>
@@ -82,6 +79,9 @@
   </si>
   <si>
     <t>ende20</t>
+  </si>
+  <si>
+    <t>$2b$10$BzVbnHXDONnHTW90gZjfQe6PPkBxGBIgh.x.1XHbwd5r8EEzqsCxi</t>
   </si>
 </sst>
 </file>
@@ -142,13 +142,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -487,6 +490,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
     <col min="27" max="27" width="3.5703125" customWidth="1"/>
     <col min="28" max="28" width="20.140625" customWidth="1"/>
     <col min="29" max="29" width="31" customWidth="1"/>
@@ -501,13 +505,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>14</v>
-      </c>
-      <c r="E1" t="s">
-        <v>15</v>
       </c>
       <c r="F1" s="5">
         <v>5</v>
@@ -555,7 +559,7 @@
         <v>19</v>
       </c>
       <c r="U1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA1" s="1"/>
     </row>
@@ -563,29 +567,29 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
+      <c r="B2" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="AA2" s="1"/>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2">
         <v>15</v>
       </c>
       <c r="AA3" s="1"/>
       <c r="AB3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC3" t="s">
         <v>5</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2">
         <f>B3*0.2</f>
@@ -603,7 +607,7 @@
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="2">
         <f>B3-B4</f>
@@ -613,7 +617,7 @@
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2">
         <f>B5-0.5*COUNTIF(B8:B20,"WAHR")</f>
@@ -623,7 +627,7 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -652,13 +656,13 @@
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
       <c r="AB7" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC7" t="s">
         <v>10</v>
       </c>
-      <c r="AC7" t="s">
+      <c r="AD7" t="s">
         <v>11</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">

--- a/website/app/dashboard/components/Kostentabelle.xlsx
+++ b/website/app/dashboard/components/Kostentabelle.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B80EF1-0C95-4B05-9B5A-8E705D5B5FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F0C36CF-FDD0-4F93-B83E-0390F4C7C161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16200" yWindow="375" windowWidth="16410" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -602,7 +602,7 @@
       </c>
       <c r="AC4" s="2">
         <f>AB4+SUM(AD8:AD33)</f>
-        <v>-200.5</v>
+        <v>-200</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="2">
         <f>B5-0.5*COUNTIF(B8:B20,"WAHR")</f>
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA6" s="1"/>
     </row>
@@ -946,7 +946,7 @@
         <v>46419</v>
       </c>
       <c r="B11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
@@ -1023,14 +1023,14 @@
       <c r="AA11" s="1"/>
       <c r="AB11" s="2">
         <f>0.5*COUNTIF($B11:Z11, "WAHR")</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AC11" s="2">
         <v>8</v>
       </c>
       <c r="AD11" s="2">
         <f t="shared" si="0"/>
-        <v>-8</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">

--- a/website/app/dashboard/components/Kostentabelle.xlsx
+++ b/website/app/dashboard/components/Kostentabelle.xlsx
@@ -1,37 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F0C36CF-FDD0-4F93-B83E-0390F4C7C161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Tabelle1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>In game Name</t>
   </si>
@@ -39,7 +22,16 @@
     <t>Edgar_</t>
   </si>
   <si>
+    <t>.test</t>
+  </si>
+  <si>
     <t xml:space="preserve">Passwort </t>
+  </si>
+  <si>
+    <t>$2b$10$BzVbnHXDONnHTW90gZjfQe6PPkBxGBIgh.x.1XHbwd5r8EEzqsCxi</t>
+  </si>
+  <si>
+    <t>$2b$10$VMWECcA6bHFcEgP5YPz21e02weZ41DqNGxa7TnMwzfZHt8keZPppi</t>
   </si>
   <si>
     <t>Geld eingezahlt</t>
@@ -68,52 +60,37 @@
   <si>
     <t>Monatsüberschuss/-defizit</t>
   </si>
-  <si>
-    <t>bla</t>
-  </si>
-  <si>
-    <t>bli</t>
-  </si>
-  <si>
-    <t>blub</t>
-  </si>
-  <si>
-    <t>ende20</t>
-  </si>
-  <si>
-    <t>$2b$10$BzVbnHXDONnHTW90gZjfQe6PPkBxGBIgh.x.1XHbwd5r8EEzqsCxi</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="[$-407]mmmm\ yy;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00 &quot;€&quot;_-;-* #,##0.00 &quot;€&quot;_-;_-* &quot;-&quot;?? &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-407]mmmm yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="3">
@@ -144,17 +121,17 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -485,9 +462,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AD34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" customWidth="1"/>
@@ -497,7 +474,7 @@
     <col min="30" max="30" width="36.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -505,168 +482,444 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="5">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="AA1" s="2"/>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5">
+      <c r="AA2" s="2"/>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5">
+      <c r="B3" s="4">
+        <v>15</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="2"/>
+      <c r="AB3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5">
+      <c r="AC3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5">
-        <v>9</v>
-      </c>
-      <c r="K1" s="5">
-        <v>10</v>
-      </c>
-      <c r="L1" s="5">
-        <v>11</v>
-      </c>
-      <c r="M1" s="5">
-        <v>12</v>
-      </c>
-      <c r="N1" s="5">
-        <v>13</v>
-      </c>
-      <c r="O1" s="5">
-        <v>14</v>
-      </c>
-      <c r="P1" s="5">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="5">
-        <v>16</v>
-      </c>
-      <c r="R1" s="5">
-        <v>17</v>
-      </c>
-      <c r="S1" s="5">
-        <v>18</v>
-      </c>
-      <c r="T1" s="5">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA1" s="1"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA2" s="1"/>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2">
-        <v>15</v>
-      </c>
-      <c r="AA3" s="1"/>
-      <c r="AB3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2">
+        <v>7</v>
+      </c>
+      <c r="B4" s="4">
         <f>B3*0.2</f>
         <v>3</v>
       </c>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="2">
+      <c r="C4" s="4">
+        <f t="shared" ref="C4:Z4" si="0">C3*0.2</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="4">
         <f>SUM($B$4:Z4)</f>
         <v>3</v>
       </c>
-      <c r="AC4" s="2">
+      <c r="AC4" s="4">
         <f>AB4+SUM(AD8:AD33)</f>
         <v>-200</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2">
+        <v>9</v>
+      </c>
+      <c r="B5" s="4">
         <f>B3-B4</f>
         <v>12</v>
       </c>
-      <c r="AA5" s="1"/>
+      <c r="C5" s="4">
+        <f t="shared" ref="C5:Z5" si="1">C3-C4</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA5" s="2"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2">
+        <v>10</v>
+      </c>
+      <c r="B6" s="4">
         <f>B5-0.5*COUNTIF(B8:B20,"WAHR")</f>
         <v>10.5</v>
       </c>
-      <c r="AA6" s="1"/>
+      <c r="C6" s="4">
+        <f t="shared" ref="C6:Z6" si="2">C5-0.5*COUNTIF(C8:C20,"WAHR")</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" si="2"/>
+        <v>-0.5</v>
+      </c>
+      <c r="E6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <f t="shared" si="2"/>
+        <v>-0.5</v>
+      </c>
+      <c r="H6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
+        <f t="shared" si="2"/>
+        <v>-0.5</v>
+      </c>
+      <c r="M6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <f t="shared" si="2"/>
+        <v>-0.5</v>
+      </c>
+      <c r="Q6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S6" s="4">
+        <f t="shared" si="2"/>
+        <v>-0.5</v>
+      </c>
+      <c r="T6" s="4">
+        <f t="shared" si="2"/>
+        <v>-0.5</v>
+      </c>
+      <c r="U6" s="4">
+        <f t="shared" si="2"/>
+        <v>-0.5</v>
+      </c>
+      <c r="V6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AA6" s="2"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="1"/>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
-      <c r="Z7" s="1"/>
-      <c r="AA7" s="1"/>
+      <c r="A7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
+      <c r="AA7" s="2"/>
       <c r="AB7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AC7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AD7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+      <c r="A8" s="6">
         <v>46296</v>
       </c>
       <c r="B8" t="b">
@@ -744,21 +997,21 @@
       <c r="Z8" t="b">
         <v>0</v>
       </c>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="2">
+      <c r="AA8" s="2"/>
+      <c r="AB8" s="4">
         <f>0.5*COUNTIF($B8:Z8, "WAHR")</f>
         <v>4</v>
       </c>
-      <c r="AC8" s="2">
+      <c r="AC8" s="4">
         <v>8</v>
       </c>
-      <c r="AD8" s="2">
+      <c r="AD8" s="4">
         <f>AB8-AC8</f>
         <v>-4</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+      <c r="A9" s="6">
         <v>46357</v>
       </c>
       <c r="B9" t="b">
@@ -836,21 +1089,21 @@
       <c r="Z9" t="b">
         <v>0</v>
       </c>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="2">
+      <c r="AA9" s="2"/>
+      <c r="AB9" s="4">
         <f>0.5*COUNTIF($B9:Z9, "WAHR")</f>
         <v>0.5</v>
       </c>
-      <c r="AC9" s="2">
+      <c r="AC9" s="4">
         <v>8</v>
       </c>
-      <c r="AD9" s="2">
-        <f t="shared" ref="AD9:AD20" si="0">AB9-AC9</f>
+      <c r="AD9" s="4">
+        <f t="shared" ref="AD9:AD20" si="3">AB9-AC9</f>
         <v>-7.5</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
+      <c r="A10" s="6">
         <v>46388</v>
       </c>
       <c r="B10" t="b">
@@ -928,21 +1181,21 @@
       <c r="Z10" t="b">
         <v>0</v>
       </c>
-      <c r="AA10" s="1"/>
-      <c r="AB10" s="2">
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="4">
         <f>0.5*COUNTIF($B10:Z10, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC10" s="2">
+      <c r="AC10" s="4">
         <v>8</v>
       </c>
-      <c r="AD10" s="2">
-        <f t="shared" si="0"/>
+      <c r="AD10" s="4">
+        <f t="shared" si="3"/>
         <v>-8</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
+      <c r="A11" s="6">
         <v>46419</v>
       </c>
       <c r="B11" t="b">
@@ -1020,21 +1273,21 @@
       <c r="Z11" t="b">
         <v>0</v>
       </c>
-      <c r="AA11" s="1"/>
-      <c r="AB11" s="2">
+      <c r="AA11" s="2"/>
+      <c r="AB11" s="4">
         <f>0.5*COUNTIF($B11:Z11, "WAHR")</f>
         <v>0.5</v>
       </c>
-      <c r="AC11" s="2">
+      <c r="AC11" s="4">
         <v>8</v>
       </c>
-      <c r="AD11" s="2">
-        <f t="shared" si="0"/>
+      <c r="AD11" s="4">
+        <f t="shared" si="3"/>
         <v>-7.5</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+      <c r="A12" s="6">
         <v>46447</v>
       </c>
       <c r="B12" t="b">
@@ -1112,21 +1365,21 @@
       <c r="Z12" t="b">
         <v>0</v>
       </c>
-      <c r="AA12" s="1"/>
-      <c r="AB12" s="2">
+      <c r="AA12" s="2"/>
+      <c r="AB12" s="4">
         <f>0.5*COUNTIF($B12:Z12, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC12" s="2">
+      <c r="AC12" s="4">
         <v>8</v>
       </c>
-      <c r="AD12" s="2">
-        <f t="shared" si="0"/>
+      <c r="AD12" s="4">
+        <f t="shared" si="3"/>
         <v>-8</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+      <c r="A13" s="6">
         <v>46478</v>
       </c>
       <c r="B13" t="b">
@@ -1204,21 +1457,21 @@
       <c r="Z13" t="b">
         <v>0</v>
       </c>
-      <c r="AA13" s="1"/>
-      <c r="AB13" s="2">
+      <c r="AA13" s="2"/>
+      <c r="AB13" s="4">
         <f>0.5*COUNTIF($B13:Z13, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC13" s="2">
+      <c r="AC13" s="4">
         <v>8</v>
       </c>
-      <c r="AD13" s="2">
-        <f t="shared" si="0"/>
+      <c r="AD13" s="4">
+        <f t="shared" si="3"/>
         <v>-8</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
+      <c r="A14" s="6">
         <v>46508</v>
       </c>
       <c r="B14" t="b">
@@ -1296,21 +1549,21 @@
       <c r="Z14" t="b">
         <v>0</v>
       </c>
-      <c r="AA14" s="1"/>
-      <c r="AB14" s="2">
+      <c r="AA14" s="2"/>
+      <c r="AB14" s="4">
         <f>0.5*COUNTIF($B14:Z14, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC14" s="2">
+      <c r="AC14" s="4">
         <v>8</v>
       </c>
-      <c r="AD14" s="2">
-        <f t="shared" si="0"/>
+      <c r="AD14" s="4">
+        <f t="shared" si="3"/>
         <v>-8</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
+      <c r="A15" s="6">
         <v>46539</v>
       </c>
       <c r="B15" t="b">
@@ -1388,21 +1641,21 @@
       <c r="Z15" t="b">
         <v>0</v>
       </c>
-      <c r="AA15" s="1"/>
-      <c r="AB15" s="2">
+      <c r="AA15" s="2"/>
+      <c r="AB15" s="4">
         <f>0.5*COUNTIF($B15:Z15, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC15" s="2">
+      <c r="AC15" s="4">
         <v>8</v>
       </c>
-      <c r="AD15" s="2">
-        <f t="shared" si="0"/>
+      <c r="AD15" s="4">
+        <f t="shared" si="3"/>
         <v>-8</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
+      <c r="A16" s="6">
         <v>46569</v>
       </c>
       <c r="B16" t="b">
@@ -1480,21 +1733,21 @@
       <c r="Z16" t="b">
         <v>0</v>
       </c>
-      <c r="AA16" s="1"/>
-      <c r="AB16" s="2">
+      <c r="AA16" s="2"/>
+      <c r="AB16" s="4">
         <f>0.5*COUNTIF($B16:Z16, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC16" s="2">
+      <c r="AC16" s="4">
         <v>8</v>
       </c>
-      <c r="AD16" s="2">
-        <f t="shared" si="0"/>
+      <c r="AD16" s="4">
+        <f t="shared" si="3"/>
         <v>-8</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+      <c r="A17" s="6">
         <v>46600</v>
       </c>
       <c r="B17" t="b">
@@ -1572,21 +1825,21 @@
       <c r="Z17" t="b">
         <v>0</v>
       </c>
-      <c r="AA17" s="1"/>
-      <c r="AB17" s="2">
+      <c r="AA17" s="2"/>
+      <c r="AB17" s="4">
         <f>0.5*COUNTIF($B17:Z17, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC17" s="2">
+      <c r="AC17" s="4">
         <v>8</v>
       </c>
-      <c r="AD17" s="2">
-        <f t="shared" si="0"/>
+      <c r="AD17" s="4">
+        <f t="shared" si="3"/>
         <v>-8</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
+      <c r="A18" s="6">
         <v>46631</v>
       </c>
       <c r="B18" t="b">
@@ -1664,21 +1917,21 @@
       <c r="Z18" t="b">
         <v>0</v>
       </c>
-      <c r="AA18" s="1"/>
-      <c r="AB18" s="2">
+      <c r="AA18" s="2"/>
+      <c r="AB18" s="4">
         <f>0.5*COUNTIF($B18:Z18, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC18" s="2">
+      <c r="AC18" s="4">
         <v>8</v>
       </c>
-      <c r="AD18" s="2">
-        <f t="shared" si="0"/>
+      <c r="AD18" s="4">
+        <f t="shared" si="3"/>
         <v>-8</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
+      <c r="A19" s="6">
         <v>46661</v>
       </c>
       <c r="B19" t="b">
@@ -1756,21 +2009,21 @@
       <c r="Z19" t="b">
         <v>0</v>
       </c>
-      <c r="AA19" s="1"/>
-      <c r="AB19" s="2">
+      <c r="AA19" s="2"/>
+      <c r="AB19" s="4">
         <f>0.5*COUNTIF($B19:Z19, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC19" s="2">
+      <c r="AC19" s="4">
         <v>8</v>
       </c>
-      <c r="AD19" s="2">
-        <f t="shared" si="0"/>
+      <c r="AD19" s="4">
+        <f t="shared" si="3"/>
         <v>-8</v>
       </c>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
+      <c r="A20" s="6">
         <v>46692</v>
       </c>
       <c r="B20" t="b">
@@ -1848,21 +2101,21 @@
       <c r="Z20" t="b">
         <v>0</v>
       </c>
-      <c r="AA20" s="1"/>
-      <c r="AB20" s="2">
+      <c r="AA20" s="2"/>
+      <c r="AB20" s="4">
         <f>0.5*COUNTIF($B20:Z20, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC20" s="2">
+      <c r="AC20" s="4">
         <v>8</v>
       </c>
-      <c r="AD20" s="2">
-        <f t="shared" si="0"/>
+      <c r="AD20" s="4">
+        <f t="shared" si="3"/>
         <v>-8</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
+      <c r="A21" s="6">
         <v>46722</v>
       </c>
       <c r="B21" t="b">
@@ -1940,21 +2193,21 @@
       <c r="Z21" t="b">
         <v>0</v>
       </c>
-      <c r="AA21" s="1"/>
-      <c r="AB21" s="2">
+      <c r="AA21" s="2"/>
+      <c r="AB21" s="4">
         <f>0.5*COUNTIF($B21:Z21, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC21" s="2">
+      <c r="AC21" s="4">
         <v>8</v>
       </c>
-      <c r="AD21" s="2">
-        <f t="shared" ref="AD21:AD33" si="1">AB21-AC21</f>
+      <c r="AD21" s="4">
+        <f t="shared" ref="AD21:AD33" si="4">AB21-AC21</f>
         <v>-8</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
+      <c r="A22" s="6">
         <v>46753</v>
       </c>
       <c r="B22" t="b">
@@ -2032,21 +2285,21 @@
       <c r="Z22" t="b">
         <v>0</v>
       </c>
-      <c r="AA22" s="1"/>
-      <c r="AB22" s="2">
+      <c r="AA22" s="2"/>
+      <c r="AB22" s="4">
         <f>0.5*COUNTIF($B22:Z22, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC22" s="2">
+      <c r="AC22" s="4">
         <v>8</v>
       </c>
-      <c r="AD22" s="2">
-        <f t="shared" si="1"/>
+      <c r="AD22" s="4">
+        <f t="shared" si="4"/>
         <v>-8</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
+      <c r="A23" s="6">
         <v>46784</v>
       </c>
       <c r="B23" t="b">
@@ -2124,21 +2377,21 @@
       <c r="Z23" t="b">
         <v>0</v>
       </c>
-      <c r="AA23" s="1"/>
-      <c r="AB23" s="2">
+      <c r="AA23" s="2"/>
+      <c r="AB23" s="4">
         <f>0.5*COUNTIF($B23:Z23, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC23" s="2">
+      <c r="AC23" s="4">
         <v>8</v>
       </c>
-      <c r="AD23" s="2">
-        <f t="shared" si="1"/>
+      <c r="AD23" s="4">
+        <f t="shared" si="4"/>
         <v>-8</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
+      <c r="A24" s="6">
         <v>46813</v>
       </c>
       <c r="B24" t="b">
@@ -2216,21 +2469,21 @@
       <c r="Z24" t="b">
         <v>0</v>
       </c>
-      <c r="AA24" s="1"/>
-      <c r="AB24" s="2">
+      <c r="AA24" s="2"/>
+      <c r="AB24" s="4">
         <f>0.5*COUNTIF($B24:Z24, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC24" s="2">
+      <c r="AC24" s="4">
         <v>8</v>
       </c>
-      <c r="AD24" s="2">
-        <f t="shared" si="1"/>
+      <c r="AD24" s="4">
+        <f t="shared" si="4"/>
         <v>-8</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
+      <c r="A25" s="6">
         <v>46844</v>
       </c>
       <c r="B25" t="b">
@@ -2308,21 +2561,21 @@
       <c r="Z25" t="b">
         <v>0</v>
       </c>
-      <c r="AA25" s="1"/>
-      <c r="AB25" s="2">
+      <c r="AA25" s="2"/>
+      <c r="AB25" s="4">
         <f>0.5*COUNTIF($B25:Z25, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC25" s="2">
+      <c r="AC25" s="4">
         <v>8</v>
       </c>
-      <c r="AD25" s="2">
-        <f t="shared" si="1"/>
+      <c r="AD25" s="4">
+        <f t="shared" si="4"/>
         <v>-8</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
+      <c r="A26" s="6">
         <v>46874</v>
       </c>
       <c r="B26" t="b">
@@ -2400,21 +2653,21 @@
       <c r="Z26" t="b">
         <v>0</v>
       </c>
-      <c r="AA26" s="1"/>
-      <c r="AB26" s="2">
+      <c r="AA26" s="2"/>
+      <c r="AB26" s="4">
         <f>0.5*COUNTIF($B26:Z26, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC26" s="2">
+      <c r="AC26" s="4">
         <v>8</v>
       </c>
-      <c r="AD26" s="2">
-        <f t="shared" si="1"/>
+      <c r="AD26" s="4">
+        <f t="shared" si="4"/>
         <v>-8</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
+      <c r="A27" s="6">
         <v>46905</v>
       </c>
       <c r="B27" t="b">
@@ -2492,21 +2745,21 @@
       <c r="Z27" t="b">
         <v>0</v>
       </c>
-      <c r="AA27" s="1"/>
-      <c r="AB27" s="2">
+      <c r="AA27" s="2"/>
+      <c r="AB27" s="4">
         <f>0.5*COUNTIF($B27:Z27, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC27" s="2">
+      <c r="AC27" s="4">
         <v>8</v>
       </c>
-      <c r="AD27" s="2">
-        <f t="shared" si="1"/>
+      <c r="AD27" s="4">
+        <f t="shared" si="4"/>
         <v>-8</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
+      <c r="A28" s="6">
         <v>46935</v>
       </c>
       <c r="B28" t="b">
@@ -2584,21 +2837,21 @@
       <c r="Z28" t="b">
         <v>0</v>
       </c>
-      <c r="AA28" s="1"/>
-      <c r="AB28" s="2">
+      <c r="AA28" s="2"/>
+      <c r="AB28" s="4">
         <f>0.5*COUNTIF($B28:Z28, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC28" s="2">
+      <c r="AC28" s="4">
         <v>8</v>
       </c>
-      <c r="AD28" s="2">
-        <f t="shared" si="1"/>
+      <c r="AD28" s="4">
+        <f t="shared" si="4"/>
         <v>-8</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
+      <c r="A29" s="6">
         <v>46966</v>
       </c>
       <c r="B29" t="b">
@@ -2676,21 +2929,21 @@
       <c r="Z29" t="b">
         <v>0</v>
       </c>
-      <c r="AA29" s="1"/>
-      <c r="AB29" s="2">
+      <c r="AA29" s="2"/>
+      <c r="AB29" s="4">
         <f>0.5*COUNTIF($B29:Z29, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC29" s="2">
+      <c r="AC29" s="4">
         <v>8</v>
       </c>
-      <c r="AD29" s="2">
-        <f t="shared" si="1"/>
+      <c r="AD29" s="4">
+        <f t="shared" si="4"/>
         <v>-8</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A30" s="4">
+      <c r="A30" s="6">
         <v>46997</v>
       </c>
       <c r="B30" t="b">
@@ -2768,21 +3021,21 @@
       <c r="Z30" t="b">
         <v>0</v>
       </c>
-      <c r="AA30" s="1"/>
-      <c r="AB30" s="2">
+      <c r="AA30" s="2"/>
+      <c r="AB30" s="4">
         <f>0.5*COUNTIF($B30:Z30, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC30" s="2">
+      <c r="AC30" s="4">
         <v>8</v>
       </c>
-      <c r="AD30" s="2">
-        <f t="shared" si="1"/>
+      <c r="AD30" s="4">
+        <f t="shared" si="4"/>
         <v>-8</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
+      <c r="A31" s="6">
         <v>47027</v>
       </c>
       <c r="B31" t="b">
@@ -2860,21 +3113,21 @@
       <c r="Z31" t="b">
         <v>0</v>
       </c>
-      <c r="AA31" s="1"/>
-      <c r="AB31" s="2">
+      <c r="AA31" s="2"/>
+      <c r="AB31" s="4">
         <f>0.5*COUNTIF($B31:Z31, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC31" s="2">
+      <c r="AC31" s="4">
         <v>8</v>
       </c>
-      <c r="AD31" s="2">
-        <f t="shared" si="1"/>
+      <c r="AD31" s="4">
+        <f t="shared" si="4"/>
         <v>-8</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A32" s="4">
+      <c r="A32" s="6">
         <v>47058</v>
       </c>
       <c r="B32" t="b">
@@ -2952,21 +3205,21 @@
       <c r="Z32" t="b">
         <v>0</v>
       </c>
-      <c r="AA32" s="1"/>
-      <c r="AB32" s="2">
+      <c r="AA32" s="2"/>
+      <c r="AB32" s="4">
         <f>0.5*COUNTIF($B32:Z32, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC32" s="2">
+      <c r="AC32" s="4">
         <v>8</v>
       </c>
-      <c r="AD32" s="2">
-        <f t="shared" si="1"/>
+      <c r="AD32" s="4">
+        <f t="shared" si="4"/>
         <v>-8</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
+      <c r="A33" s="6">
         <v>47088</v>
       </c>
       <c r="B33" t="b">
@@ -3044,23 +3297,23 @@
       <c r="Z33" t="b">
         <v>0</v>
       </c>
-      <c r="AA33" s="1"/>
-      <c r="AB33" s="2">
+      <c r="AA33" s="2"/>
+      <c r="AB33" s="4">
         <f>0.5*COUNTIF($B33:Z33, "WAHR")</f>
         <v>0</v>
       </c>
-      <c r="AC33" s="2">
+      <c r="AC33" s="4">
         <v>8</v>
       </c>
-      <c r="AD33" s="2">
-        <f t="shared" si="1"/>
+      <c r="AD33" s="4">
+        <f t="shared" si="4"/>
         <v>-8</v>
       </c>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/website/app/dashboard/components/Kostentabelle.xlsx
+++ b/website/app/dashboard/components/Kostentabelle.xlsx
@@ -926,7 +926,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>

--- a/website/app/dashboard/components/Kostentabelle.xlsx
+++ b/website/app/dashboard/components/Kostentabelle.xlsx
@@ -1,20 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8BA11A-BF5A-4F57-BC69-B3987B4704F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Tabelle1" state="visible" r:id="rId4"/>
+    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>In game Name</t>
   </si>
@@ -25,6 +42,9 @@
     <t>.test</t>
   </si>
   <si>
+    <t>Javatest</t>
+  </si>
+  <si>
     <t xml:space="preserve">Passwort </t>
   </si>
   <si>
@@ -32,6 +52,9 @@
   </si>
   <si>
     <t>$2b$10$VMWECcA6bHFcEgP5YPz21e02weZ41DqNGxa7TnMwzfZHt8keZPppi</t>
+  </si>
+  <si>
+    <t>$2b$10$Mbmx0KfbHMWvv62pSIgDQuSZhz3OxuOc2Pn7XYZxdBOlzs3CMWRuG</t>
   </si>
   <si>
     <t>Geld eingezahlt</t>
@@ -64,33 +87,33 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00 &quot;€&quot;_-;-* #,##0.00 &quot;€&quot;_-;_-* &quot;-&quot;?? &quot;€&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-407]mmmm yy;@"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="[$-407]mmmm\ yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="3">
@@ -126,12 +149,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -462,9 +485,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD34"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" customWidth="1"/>
@@ -474,7 +497,7 @@
     <col min="30" max="30" width="36.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -483,6 +506,9 @@
       </c>
       <c r="C1" t="s">
         <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -501,67 +527,118 @@
       <c r="T1" s="1"/>
       <c r="AA1" s="2"/>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
       <c r="AA2" s="2"/>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="4">
         <v>15</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4"/>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0</v>
+      </c>
+      <c r="R3" s="4">
+        <v>0</v>
+      </c>
+      <c r="S3" s="4">
+        <v>0</v>
+      </c>
+      <c r="T3" s="4">
+        <v>0</v>
+      </c>
+      <c r="U3" s="4">
+        <v>0</v>
+      </c>
+      <c r="V3" s="4">
+        <v>0</v>
+      </c>
+      <c r="W3" s="4">
+        <v>0</v>
+      </c>
+      <c r="X3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="4">
+        <v>0</v>
+      </c>
       <c r="AA3" s="2"/>
       <c r="AB3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" s="4">
-        <f>B3*0.2</f>
+        <f t="shared" ref="B4:Y4" si="0">IF(B3*0.2=0,0,B3*0.2)</f>
         <v>3</v>
       </c>
       <c r="C4" s="4">
-        <f t="shared" ref="C4:Z4" si="0">C3*0.2</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D4" s="4">
@@ -653,7 +730,7 @@
         <v>0</v>
       </c>
       <c r="Z4" s="4">
-        <f t="shared" si="0"/>
+        <f>IF(Z3*0.2=0,0,Z3*0.2)</f>
         <v>0</v>
       </c>
       <c r="AA4" s="2"/>
@@ -663,19 +740,19 @@
       </c>
       <c r="AC4" s="4">
         <f>AB4+SUM(AD8:AD33)</f>
-        <v>-200</v>
+        <v>-203.5</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" s="4">
-        <f>B3-B4</f>
+        <f t="shared" ref="B5:Y5" si="1">IF(B3-B4=0,0,B3-B4)</f>
         <v>12</v>
       </c>
       <c r="C5" s="4">
-        <f t="shared" ref="C5:Z5" si="1">C3-C4</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D5" s="4">
@@ -767,26 +844,26 @@
         <v>0</v>
       </c>
       <c r="Z5" s="4">
-        <f t="shared" si="1"/>
+        <f>IF(Z3-Z4=0,0,Z3-Z4)</f>
         <v>0</v>
       </c>
       <c r="AA5" s="2"/>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4">
-        <f>B5-0.5*COUNTIF(B8:B20,"WAHR")</f>
+        <f>IF(B5-0.5*COUNTIF(B8:B33,"WAHR")=0,0,(B5-0.5*COUNTIF(B8:B33,"WAHR")))</f>
         <v>10.5</v>
       </c>
       <c r="C6" s="4">
-        <f t="shared" ref="C6:Z6" si="2">C5-0.5*COUNTIF(C8:C20,"WAHR")</f>
+        <f>IF(C5-0.5*COUNTIF(C8:C33,"WAHR")=0,0,(C5-0.5*COUNTIF(C8:C33,"WAHR")))</f>
         <v>0</v>
       </c>
       <c r="D6" s="4">
-        <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <f t="shared" ref="D6:Z6" si="2">IF(D5-0.5*COUNTIF(D8:D33,"WAHR")=0,0,(D5-0.5*COUNTIF(D8:D33,"WAHR")))</f>
+        <v>0</v>
       </c>
       <c r="E6" s="4">
         <f t="shared" si="2"/>
@@ -798,7 +875,7 @@
       </c>
       <c r="G6" s="4">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="2"/>
@@ -818,7 +895,7 @@
       </c>
       <c r="L6" s="4">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="M6" s="4">
         <f t="shared" si="2"/>
@@ -834,7 +911,7 @@
       </c>
       <c r="P6" s="4">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="4">
         <f t="shared" si="2"/>
@@ -846,15 +923,15 @@
       </c>
       <c r="S6" s="4">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="T6" s="4">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="U6" s="4">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="V6" s="4">
         <f t="shared" si="2"/>
@@ -880,7 +957,7 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -909,13 +986,13 @@
       <c r="Z7" s="2"/>
       <c r="AA7" s="2"/>
       <c r="AB7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AC7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AD7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
@@ -926,10 +1003,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -938,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -953,7 +1030,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -965,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
@@ -974,13 +1051,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="b">
         <v>0</v>
@@ -1000,14 +1077,14 @@
       <c r="AA8" s="2"/>
       <c r="AB8" s="4">
         <f>0.5*COUNTIF($B8:Z8, "WAHR")</f>
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="AC8" s="4">
         <v>8</v>
       </c>
       <c r="AD8" s="4">
         <f>AB8-AC8</f>
-        <v>-4</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
@@ -3310,10 +3387,10 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="6"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>